--- a/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件三.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件三.xlsx
@@ -1,179 +1,754 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="184">
+  <si>
+    <t>角色编号</t>
+  </si>
+  <si>
+    <t>台词编号</t>
+  </si>
+  <si>
+    <t>台词 / 旁白文本</t>
+  </si>
+  <si>
+    <t>立绘 / 动作提示</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>午后，阳光正好</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>你挑了一个离家不远的公园，换上舒服的运动鞋，带了一本书，打算找一个景致优美的地方，安安静静地过一个下午</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>许是工作日的缘故，整个公园被静谧笼罩。偶尔有一两个遛狗的老人经过，脚步慢悠悠的，像是在和时间商量着什么</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>可是安静的有些过了头，习惯了城市喧嚣的你，在这种绝对的安静里，反而觉得有些空落落的</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>可惜许映月还在苦命地上班，你打开微信，看见她三小时前发的一条朋友圈：“甲方又要改需求，我要死了。”</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>你犹豫了一下，没敢打扰她。很自然的，你就想起时安</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>你打开那个陪玩 App，看见他的黑色头像亮着，就顺手下了两小时的闲聊单</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>语音刚接通，耳机里传来的却不是他往日那般从容温润的开场白，而是一阵沉重且急促的喘息</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>背景音里还夹杂着呼啸的风声和手推车滚轮摩擦地面的轰隆声</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>“呼…… 老板，下午好。抱歉，刚才风有点大，今天想聊点什么？”</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>他的语速比平时快了些，尾音里带着一丝显而易见的沙哑和虚浮</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>他在极力调整呼吸，试图把那种疲惫感强压下去，重新披上那层完美且游刃有余的外衣</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>作为常年和各种情绪打交道的自媒体人，你瞬间就察觉到了他的不对劲</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>他现在的状态，就像是一根已经崩到极限、随时会断裂的弦</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>你没有戳破他的勉强，只是把语气放得更平和、更随意了一些，像是真的什么都没察觉到</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>“没什么特别想聊的，我在公园采风，只是想找个人连着麦。你在外面？”</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>那头沉默了两秒，然后他的声音响起，带着一丝窘迫，但很快就被压了下去</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>“嗯，接了个同城搬运的兼职。不影响的，老板可以说说你那边的风景，我听着呢。”</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>他说话的时候，背景里传来一声沉闷的重物落地声，像是他把什么东西放下了，然后长长地呼了一口气</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>你没有追问，开始随口向他描述公园里晒太阳的流浪猫、落在地上歇脚的喜鹊、从容路过的行人</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>起初，他还能用那些恰到好处的温柔话语回应你</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>但渐渐地，他的回应变成了单音节的 “嗯”、“是吗”，甚至好几次出现了长达十几秒的空白</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>听筒里传来的，只有他越来越沉重的呼吸声，以及某种重物被艰难放下的闷响</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>大概又过了十秒，他的声音才再次响起，比之前更低、更哑</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>“……听起来真好啊。”</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>他说真好的时候，声音里有一种很奇怪的东西，有一种隔着玻璃看别人家的灯火的怅然</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>这种透过网线传来的、几乎要令人窒息的疲惫感，让你不自觉地皱起了眉头</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>你们虽然有过几次不错的交流，但还只是雇佣关系，你不打算越界去窥探一个年轻人的窘迫</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>你看了眼时间，已经过了四十分钟，或许是时候做出了一个成熟体贴的决定</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>“时安，我这边也没什么事了。听得出你今天很累，这单就先到这里吧。”</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>你顿了顿，又补了一句</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>“你不用有负担，我会照常结算。去买瓶水，找个阴凉的地方歇一会儿吧。”</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>你准备按下挂断键，但就在你的手指即将触碰到屏幕的那一刻</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>“老板！等等……”</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>你停住了动作，但那头陷入的沉默几乎让你以为已经挂断了</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>过了好一会儿，你听到他像是脱力一般，顺着墙壁滑坐下去的摩擦声</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>当他再次开口时，那层完美服务者的坚硬外壳已经彻底粉碎</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>他的声音带着一种生怕被拒绝的小心翼翼，甚至透出一丝不易察觉的哀求</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>“……可以不挂吗？就十分钟。我可以把钱退给你……我只是，现在真的很想再听听你的声音。”</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>左右现在也没什么急事，你没有接受，也没有拒绝</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>在你的不带评判、充满包容的沉默里，他安静了下来</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>过了大概两分钟，他的声音才再次响起，比之前稳了一些，但依然带着一种不加掩饰的疲惫</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>“老板你不用给我结算。”</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>他的声音很轻，像是在自言自语</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>“我刚才什么都没做，光听你说话了。不对，现在是你听我说了。”</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>你坐在公园的长椅上，阳光透过银杏叶的缝隙，在你的手背上投下斑驳的光影</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>他好像有点语无伦次，或许需要你适时地引导话题。你想了想，随口一问</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>“时安，你在哪里兼职？”</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>在你的引导下，他慢慢平复了呼吸，开始断断续续地说起自己的生活</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>“物流园的兼职、学校图书馆的整理工作、给初中生补课的周末。三份工，日结，不耽误上课。”</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>你说不清自己是什么感觉，大概是一种敬意</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>“平时都看什么书？”</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>“啊？”</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>“你说图书馆的活儿能顺便看书，你都看什么？”</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>他没想到你会问这个问题，沉默了一下，似乎停下了手头的工作开始回想</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>“最近在看《被讨厌的勇气》，里面有一句话我记了很久——‘重要的不是被给予了什么，而是如何去利用被给予的东西’。”</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>他说这句话的时候，声音里有一种很深的确认感，像是溺水的人终于抓住了一根浮木</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>“或许另外一本书也很适合你。”</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>“哪本？”</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>“维克多・弗兰克尔的《活出生命的意义》”</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>“‘人所拥有的任何东西，都可以被剥夺，唯独人性最后的自由，选择自己态度和生活方式的自由，不能被剥夺’。”</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>电话那头安静了很久，才听到他很轻很轻的答复声</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>“……我记住了，谢谢。”</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>你无意深入了解他的遭遇抑或是境遇，但没有谁是一座孤岛</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>千百小时的倾听，可能他自己也没意识到，他也想被听到</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>【抉择选项】意有所指的回复</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>你靠在长椅上，树上的银杏叶从你眼前飘落</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>“你能靠自己打三份工攒学费，说明你已经具备了独立生存的能力。不要回头看那些不值得的人和事，向前走就是了。”</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>不知又是触发了他什么回忆，呼吸声明显急促了片刻，随后，他长长地呼出一口气</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>“你说得对，只有攥在自己手里的未来才是真的。老板，谢谢你。”</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>他的声音褪去了脆弱，重新变得坚定</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>“嗯，去吧。”</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>挂断电话后，你收到了平台退款到账的通知，还有时安发过来的红包</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>备注是：感谢老板的倾听，一点小小的心意，还请收下。</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>你没有跟他客气，点开收了</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>一方面，这是你应得的。另一方面，你也知道，这是他的方式</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>他不习惯被给予，在平等的关系中能找到一点安全感，接受他的好意，才是对他的尊重</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>【抉择选项】给予情感上的回应</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>你听着他的话，风从湖面上吹过来，带着水汽的凉意</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>你开口，声音比平时轻了一些</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>“你不需要向我道谢，我不知道你的过去，但能在那种环境里靠自己走出来，时安，你已经比大多数人都厉害了。”</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>又是一段长时间的静默，你下意识看了看手机，确认电话没有挂断</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>片刻后他的声音再次响起时，不知是不是错觉，你感觉他的声音有些哽咽</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>“……从小到大，从来没有人对我说过这些。”</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>“好好生活，比什么都重要。”</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>他很轻的应了一声</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>“好。”</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>风再次掠过枝头，带起一阵轻响，刚刚翻涌的情绪被悄悄藏进了沉默里</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,156 +1048,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,74 +1256,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1512,1083 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D89"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="114" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>